--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486562_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486562_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.8057</v>
+        <v>6.8174</v>
       </c>
       <c r="E2" t="n">
-        <v>7.2437</v>
+        <v>6.0396</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.7776999999999999</v>
       </c>
       <c r="G2" t="n">
         <v>4.9917</v>
@@ -610,13 +610,13 @@
         <v>0.6525</v>
       </c>
       <c r="S2" t="n">
-        <v>2.1615</v>
+        <v>1.1732</v>
       </c>
       <c r="T2" t="n">
-        <v>2.0982</v>
+        <v>0.8941</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0633</v>
+        <v>0.2791</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.8351</v>
+        <v>5.9036</v>
       </c>
       <c r="E3" t="n">
-        <v>4.5394</v>
+        <v>4.6079</v>
       </c>
       <c r="F3" t="n">
         <v>1.2957</v>
@@ -688,10 +688,10 @@
         <v>1.0875</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4795</v>
+        <v>0.548</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1971</v>
+        <v>0.2656</v>
       </c>
       <c r="U3" t="n">
         <v>0.2824</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. MUÑOZ BORCHERS</t>
+          <t>I. JAKOVICS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.2862</v>
+        <v>5.4541</v>
       </c>
       <c r="E4" t="n">
-        <v>3.7524</v>
+        <v>3.7379</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5337</v>
+        <v>1.7163</v>
       </c>
       <c r="G4" t="n">
-        <v>3.6986</v>
+        <v>5.2838</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3526</v>
+        <v>1.1162</v>
       </c>
       <c r="I4" t="n">
-        <v>3.346</v>
+        <v>4.1676</v>
       </c>
       <c r="J4" t="n">
-        <v>3.6239</v>
+        <v>4.9445</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6205000000000001</v>
+        <v>1.8646</v>
       </c>
       <c r="L4" t="n">
-        <v>3.0034</v>
+        <v>3.0799</v>
       </c>
       <c r="M4" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.3393</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2679</v>
+        <v>-0.7484</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3426</v>
+        <v>1.0877</v>
       </c>
       <c r="P4" t="n">
-        <v>1.305</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-3.2626</v>
       </c>
       <c r="R4" t="n">
-        <v>1.305</v>
+        <v>1.7401</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2825</v>
+        <v>0.3677</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1286</v>
+        <v>0.1658</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1539</v>
+        <v>0.2019</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.3252</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.8902</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. VRANKIC</t>
+          <t>A. MUÑOZ BORCHERS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.9076</v>
+        <v>5.2737</v>
       </c>
       <c r="E5" t="n">
-        <v>3.3341</v>
+        <v>3.7092</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5735</v>
+        <v>1.5646</v>
       </c>
       <c r="G5" t="n">
-        <v>1.0959</v>
+        <v>3.6986</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.2006</v>
+        <v>0.3526</v>
       </c>
       <c r="I5" t="n">
-        <v>1.2965</v>
+        <v>3.346</v>
       </c>
       <c r="J5" t="n">
-        <v>1.8531</v>
+        <v>3.6239</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0283</v>
+        <v>0.6205000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8248</v>
+        <v>3.0034</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.7572</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.2289</v>
+        <v>-0.2679</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4717</v>
+        <v>0.3426</v>
       </c>
       <c r="P5" t="n">
-        <v>0.435</v>
+        <v>1.305</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5225</v>
+        <v>1.305</v>
       </c>
       <c r="S5" t="n">
-        <v>1.6818</v>
+        <v>0.2701</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8736</v>
+        <v>0.0853</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8081</v>
+        <v>0.1847</v>
       </c>
       <c r="V5" t="n">
-        <v>1.695</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.695</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>I. JAKOVICS</t>
+          <t>J. VRANKIC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4.6033</v>
+        <v>4.8905</v>
       </c>
       <c r="E6" t="n">
-        <v>2.8871</v>
+        <v>3.4711</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7163</v>
+        <v>1.4194</v>
       </c>
       <c r="G6" t="n">
-        <v>5.2838</v>
+        <v>1.0959</v>
       </c>
       <c r="H6" t="n">
-        <v>1.1162</v>
+        <v>-0.2006</v>
       </c>
       <c r="I6" t="n">
-        <v>4.1676</v>
+        <v>1.2965</v>
       </c>
       <c r="J6" t="n">
-        <v>4.9445</v>
+        <v>1.8531</v>
       </c>
       <c r="K6" t="n">
-        <v>1.8646</v>
+        <v>1.0283</v>
       </c>
       <c r="L6" t="n">
-        <v>3.0799</v>
+        <v>0.8248</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3393</v>
+        <v>-0.7572</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7484</v>
+        <v>-1.2289</v>
       </c>
       <c r="O6" t="n">
-        <v>1.0877</v>
+        <v>0.4717</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.5225</v>
+        <v>0.435</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.2626</v>
+        <v>-1.0875</v>
       </c>
       <c r="R6" t="n">
-        <v>1.7401</v>
+        <v>1.5225</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4831</v>
+        <v>1.6646</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6850000000000001</v>
+        <v>1.0106</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2019</v>
+        <v>0.654</v>
       </c>
       <c r="V6" t="n">
-        <v>1.3252</v>
+        <v>1.695</v>
       </c>
       <c r="W6" t="n">
-        <v>1.8902</v>
+        <v>1.695</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. ARMUS</t>
+          <t>X. OROZ URIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,40 +955,40 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.4292</v>
+        <v>3.3183</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8784999999999999</v>
+        <v>2.2455</v>
       </c>
       <c r="F7" t="n">
-        <v>2.5506</v>
+        <v>1.0728</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0556</v>
+        <v>1.1681</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4867</v>
+        <v>1.4598</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4311</v>
+        <v>-0.2917</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2807</v>
+        <v>1.8249</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1277</v>
+        <v>1.8432</v>
       </c>
       <c r="L7" t="n">
-        <v>0.153</v>
+        <v>-0.0183</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3364</v>
+        <v>-0.6567</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6143999999999999</v>
+        <v>-0.3834</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2781</v>
+        <v>-0.2733</v>
       </c>
       <c r="P7" t="n">
         <v>1.0875</v>
@@ -1000,28 +1000,28 @@
         <v>1.0875</v>
       </c>
       <c r="S7" t="n">
-        <v>1.6577</v>
+        <v>1.2579</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4026</v>
+        <v>0.4206</v>
       </c>
       <c r="U7" t="n">
-        <v>1.2552</v>
+        <v>0.8373</v>
       </c>
       <c r="V7" t="n">
-        <v>0.7395</v>
+        <v>-0.1952</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5443</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X. OROZ URIA</t>
+          <t>M. ARMUS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,40 +1033,40 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>3.0503</v>
+        <v>3.0353</v>
       </c>
       <c r="E8" t="n">
-        <v>1.885</v>
+        <v>0.947</v>
       </c>
       <c r="F8" t="n">
-        <v>1.1653</v>
+        <v>2.0883</v>
       </c>
       <c r="G8" t="n">
-        <v>1.1681</v>
+        <v>-0.0556</v>
       </c>
       <c r="H8" t="n">
-        <v>1.4598</v>
+        <v>-0.4867</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2917</v>
+        <v>0.4311</v>
       </c>
       <c r="J8" t="n">
-        <v>1.8249</v>
+        <v>0.2807</v>
       </c>
       <c r="K8" t="n">
-        <v>1.8432</v>
+        <v>0.1277</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.0183</v>
+        <v>0.153</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.6567</v>
+        <v>-0.3364</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3834</v>
+        <v>-0.6143999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2733</v>
+        <v>0.2781</v>
       </c>
       <c r="P8" t="n">
         <v>1.0875</v>
@@ -1078,22 +1078,22 @@
         <v>1.0875</v>
       </c>
       <c r="S8" t="n">
-        <v>0.9898</v>
+        <v>1.2639</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0601</v>
+        <v>0.4711</v>
       </c>
       <c r="U8" t="n">
-        <v>0.9297</v>
+        <v>0.7927999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.1952</v>
+        <v>0.7395</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1952</v>
+        <v>0.5443</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2714</v>
+        <v>0.649</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0955</v>
+        <v>0.319</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1758</v>
+        <v>0.33</v>
       </c>
       <c r="G9" t="n">
         <v>-1.61</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5738</v>
+        <v>-0.1962</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.274</v>
+        <v>-0.0505</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2998</v>
+        <v>-0.1457</v>
       </c>
       <c r="V9" t="n">
         <v>2.4552</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0014</v>
+        <v>0.0902</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2423</v>
+        <v>-0.3973</v>
       </c>
       <c r="F10" t="n">
-        <v>0.241</v>
+        <v>0.4875</v>
       </c>
       <c r="G10" t="n">
         <v>-1.5291</v>
@@ -1234,13 +1234,13 @@
         <v>2.1751</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6355</v>
+        <v>0.727</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8051</v>
+        <v>0.6501</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1697</v>
+        <v>0.0769</v>
       </c>
       <c r="V10" t="n">
         <v>-0.1952</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>V. VUCETIC</t>
+          <t>A. KUNKEL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.4737</v>
+        <v>-0.3332</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.1804</v>
+        <v>0.2953</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7068</v>
+        <v>-0.6284999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.6574</v>
+        <v>0.9276</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1977</v>
+        <v>-0.4956</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.8551</v>
+        <v>1.4232</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.0541</v>
+        <v>1.9008</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6966</v>
+        <v>1.2473</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.7507</v>
+        <v>0.6535</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.6032999999999999</v>
+        <v>-0.9732</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4989</v>
+        <v>-1.7429</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1044</v>
+        <v>0.7697000000000001</v>
       </c>
       <c r="P11" t="n">
-        <v>1.305</v>
+        <v>-0.435</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R11" t="n">
-        <v>1.305</v>
+        <v>1.7401</v>
       </c>
       <c r="S11" t="n">
-        <v>0.8787</v>
+        <v>0.8691</v>
       </c>
       <c r="T11" t="n">
-        <v>0.8736</v>
+        <v>0.5696</v>
       </c>
       <c r="U11" t="n">
-        <v>0.005</v>
+        <v>0.2995</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-1.695</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. KUNKEL</t>
+          <t>V. VUCETIC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.9269</v>
+        <v>-0.8338</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.9593</v>
+        <v>-1.6022</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.9676</v>
+        <v>0.7684</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9276</v>
+        <v>-2.6574</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4956</v>
+        <v>0.1977</v>
       </c>
       <c r="I12" t="n">
-        <v>1.4232</v>
+        <v>-2.8551</v>
       </c>
       <c r="J12" t="n">
-        <v>1.9008</v>
+        <v>-2.0541</v>
       </c>
       <c r="K12" t="n">
-        <v>1.2473</v>
+        <v>0.6966</v>
       </c>
       <c r="L12" t="n">
-        <v>0.6535</v>
+        <v>-2.7507</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.9732</v>
+        <v>-0.6032999999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.7429</v>
+        <v>-0.4989</v>
       </c>
       <c r="O12" t="n">
-        <v>0.7697000000000001</v>
+        <v>-0.1044</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.435</v>
+        <v>1.305</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.7401</v>
+        <v>1.305</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7245</v>
+        <v>0.5185</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6850000000000001</v>
+        <v>0.4518</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0395</v>
+        <v>0.0667</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.695</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.695</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.3415</v>
+        <v>-2.7924</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.9344</v>
+        <v>-3.0462</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5929</v>
+        <v>0.2538</v>
       </c>
       <c r="G13" t="n">
         <v>1.9415</v>
@@ -1468,13 +1468,13 @@
         <v>0.435</v>
       </c>
       <c r="S13" t="n">
-        <v>1.1319</v>
+        <v>0.6811</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4711</v>
+        <v>0.3593</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6608000000000001</v>
+        <v>0.3217</v>
       </c>
       <c r="V13" t="n">
         <v>-1.4997</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>30.4453</v>
+        <v>31.4727</v>
       </c>
       <c r="E14" t="n">
-        <v>19.2993</v>
+        <v>20.3268</v>
       </c>
       <c r="F14" t="n">
         <v>11.146</v>
       </c>
       <c r="G14" t="n">
-        <v>16.9375</v>
+        <v>16.93750000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>3.649800000000001</v>
+        <v>3.6498</v>
       </c>
       <c r="I14" t="n">
         <v>13.2876</v>
@@ -1525,7 +1525,7 @@
         <v>11.1335</v>
       </c>
       <c r="L14" t="n">
-        <v>9.215999999999999</v>
+        <v>9.215999999999998</v>
       </c>
       <c r="M14" t="n">
         <v>-3.411999999999999</v>
@@ -1546,10 +1546,10 @@
         <v>14.1378</v>
       </c>
       <c r="S14" t="n">
-        <v>8.1175</v>
+        <v>9.144900000000002</v>
       </c>
       <c r="T14" t="n">
-        <v>4.265999999999999</v>
+        <v>5.293400000000001</v>
       </c>
       <c r="U14" t="n">
         <v>3.8513</v>
@@ -1558,7 +1558,7 @@
         <v>3.2155</v>
       </c>
       <c r="W14" t="n">
-        <v>6.646799999999999</v>
+        <v>6.646800000000001</v>
       </c>
       <c r="X14" t="n">
         <v>-3.4313</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5441</v>
+        <v>1.731</v>
       </c>
       <c r="E15" t="n">
-        <v>3.8118</v>
+        <v>3.0295</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.2678</v>
+        <v>-1.2986</v>
       </c>
       <c r="G15" t="n">
         <v>2.9686</v>
@@ -1624,13 +1624,13 @@
         <v>1.7401</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2945</v>
+        <v>-1.1077</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3257</v>
+        <v>-0.4566</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6202</v>
+        <v>-0.651</v>
       </c>
       <c r="V15" t="n">
         <v>-0.5649999999999999</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. KANDE KIELI</t>
+          <t>R. JOHNSON JR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0027</v>
+        <v>-0.4186</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4199</v>
+        <v>0.3265</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.4226</v>
+        <v>-0.7452</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.8369</v>
+        <v>1.6132</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.2527</v>
+        <v>1.7702</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.5842</v>
+        <v>-0.157</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.2741</v>
+        <v>3.1888</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.3888</v>
+        <v>2.2875</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1147</v>
+        <v>0.9013</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.5628</v>
+        <v>-1.5756</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8639</v>
+        <v>-0.5173</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.6989</v>
+        <v>-1.0583</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.2175</v>
+        <v>-0.87</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0875</v>
+        <v>-2.3926</v>
       </c>
       <c r="R16" t="n">
-        <v>0.87</v>
+        <v>1.5225</v>
       </c>
       <c r="S16" t="n">
-        <v>1.7472</v>
+        <v>-1.5316</v>
       </c>
       <c r="T16" t="n">
-        <v>2.0213</v>
+        <v>-1.0346</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2741</v>
+        <v>-0.4969</v>
       </c>
       <c r="V16" t="n">
-        <v>1.3045</v>
+        <v>0.3698</v>
       </c>
       <c r="W16" t="n">
-        <v>0.7602</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X16" t="n">
-        <v>0.5443</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. JOHNSON JR</t>
+          <t>J. POWELL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,40 +1735,40 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.8155</v>
+        <v>-0.5785</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.008699999999999999</v>
+        <v>0.5648</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8068</v>
+        <v>-1.1433</v>
       </c>
       <c r="G17" t="n">
-        <v>1.6132</v>
+        <v>1.4645</v>
       </c>
       <c r="H17" t="n">
-        <v>1.7702</v>
+        <v>0.8971</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.157</v>
+        <v>0.5674</v>
       </c>
       <c r="J17" t="n">
-        <v>3.1888</v>
+        <v>2.2105</v>
       </c>
       <c r="K17" t="n">
-        <v>2.2875</v>
+        <v>1.1164</v>
       </c>
       <c r="L17" t="n">
-        <v>0.9013</v>
+        <v>1.0941</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.5756</v>
+        <v>-0.7461</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5173</v>
+        <v>-0.2193</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.0583</v>
+        <v>-0.5268</v>
       </c>
       <c r="P17" t="n">
         <v>-0.87</v>
@@ -1780,28 +1780,28 @@
         <v>1.5225</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.9285</v>
+        <v>-1.5427</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.3699</v>
+        <v>-0.9481000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5586</v>
+        <v>-0.5946</v>
       </c>
       <c r="V17" t="n">
         <v>0.3698</v>
       </c>
       <c r="W17" t="n">
-        <v>0.5649999999999999</v>
+        <v>1.695</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1952</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. POWELL</t>
+          <t>G. KANDE KIELI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.2297</v>
+        <v>-1.4864</v>
       </c>
       <c r="E18" t="n">
-        <v>0.006</v>
+        <v>-0.033</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.2357</v>
+        <v>-1.4534</v>
       </c>
       <c r="G18" t="n">
-        <v>1.4645</v>
+        <v>-2.8369</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8971</v>
+        <v>-1.2527</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5674</v>
+        <v>-1.5842</v>
       </c>
       <c r="J18" t="n">
-        <v>2.2105</v>
+        <v>-0.2741</v>
       </c>
       <c r="K18" t="n">
-        <v>1.1164</v>
+        <v>-0.3888</v>
       </c>
       <c r="L18" t="n">
-        <v>1.0941</v>
+        <v>0.1147</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7461</v>
+        <v>-2.5628</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2193</v>
+        <v>-0.8639</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5268</v>
+        <v>-1.6989</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.87</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.3926</v>
+        <v>-1.0875</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5225</v>
+        <v>0.87</v>
       </c>
       <c r="S18" t="n">
-        <v>-2.1939</v>
+        <v>0.2635</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.5069</v>
+        <v>0.5684</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6870000000000001</v>
+        <v>-0.3049</v>
       </c>
       <c r="V18" t="n">
-        <v>0.3698</v>
+        <v>1.3045</v>
       </c>
       <c r="W18" t="n">
-        <v>1.695</v>
+        <v>0.7602</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.3252</v>
+        <v>0.5443</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.3395</v>
+        <v>-1.8809</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2103</v>
+        <v>-0.875</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1292</v>
+        <v>-1.0059</v>
       </c>
       <c r="G19" t="n">
         <v>-1.3461</v>
@@ -1936,13 +1936,13 @@
         <v>0.2175</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.2108</v>
+        <v>-0.7523</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6165</v>
+        <v>-0.2812</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5944</v>
+        <v>-0.4711</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.0348</v>
+        <v>-4.6322</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.0362</v>
+        <v>-3.8185</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.9986</v>
+        <v>-0.8137</v>
       </c>
       <c r="G20" t="n">
         <v>0.1847</v>
@@ -2014,13 +2014,13 @@
         <v>1.5225</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6302</v>
+        <v>-1.2275</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1887</v>
+        <v>-0.5936</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8188</v>
+        <v>-0.6339</v>
       </c>
       <c r="V20" t="n">
         <v>-0.5443</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.9745</v>
+        <v>-4.9668</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3769</v>
+        <v>-1.1534</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.5976</v>
+        <v>-3.8133</v>
       </c>
       <c r="G21" t="n">
         <v>-3.4457</v>
@@ -2092,13 +2092,13 @@
         <v>0.87</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4863</v>
+        <v>-0.4786</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6934</v>
+        <v>-0.4698</v>
       </c>
       <c r="U21" t="n">
-        <v>0.207</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="V21" t="n">
         <v>-1.695</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.198</v>
+        <v>-5.6006</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.8608</v>
+        <v>-3.0785</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.3372</v>
+        <v>-2.5222</v>
       </c>
       <c r="G22" t="n">
         <v>-5.4102</v>
@@ -2170,13 +2170,13 @@
         <v>1.9576</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.6579</v>
+        <v>-1.0605</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.4384</v>
+        <v>-0.6561</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2194</v>
+        <v>-0.4044</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.2273</v>
+        <v>-5.8727</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.5547</v>
+        <v>-4.1077</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.6725</v>
+        <v>-1.765</v>
       </c>
       <c r="G23" t="n">
         <v>-5.3761</v>
@@ -2248,13 +2248,13 @@
         <v>0.87</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6337</v>
+        <v>-0.2791</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6165</v>
+        <v>-0.1694</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0172</v>
+        <v>-0.1097</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.1673</v>
+        <v>-6.7396</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.336</v>
+        <v>-2.0007</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.8314</v>
+        <v>-4.7389</v>
       </c>
       <c r="G24" t="n">
         <v>-4.7534</v>
@@ -2326,13 +2326,13 @@
         <v>0.87</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8288</v>
+        <v>-0.4011</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1454</v>
+        <v>0.1899</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6834</v>
+        <v>-0.5909</v>
       </c>
       <c r="V24" t="n">
         <v>-2.4552</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-30.4452</v>
+        <v>-30.4453</v>
       </c>
       <c r="E25" t="n">
-        <v>-11.1459</v>
+        <v>-11.146</v>
       </c>
       <c r="F25" t="n">
-        <v>-19.2994</v>
+        <v>-19.2995</v>
       </c>
       <c r="G25" t="n">
         <v>-16.9374</v>
@@ -2380,7 +2380,7 @@
         <v>3.412000000000003</v>
       </c>
       <c r="K25" t="n">
-        <v>7.483600000000001</v>
+        <v>7.4836</v>
       </c>
       <c r="L25" t="n">
         <v>-4.0718</v>
@@ -2404,10 +2404,10 @@
         <v>11.9627</v>
       </c>
       <c r="S25" t="n">
-        <v>-8.117400000000002</v>
+        <v>-8.117599999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>-3.8513</v>
+        <v>-3.8511</v>
       </c>
       <c r="U25" t="n">
         <v>-4.2661</v>
@@ -2416,7 +2416,7 @@
         <v>-3.2154</v>
       </c>
       <c r="W25" t="n">
-        <v>3.431299999999999</v>
+        <v>3.4313</v>
       </c>
       <c r="X25" t="n">
         <v>-6.646699999999999</v>
